--- a/public/templates/cha-jewels-product-upload-template.xlsx
+++ b/public/templates/cha-jewels-product-upload-template.xlsx
@@ -1156,7 +1156,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AF204"/>
+  <dimension ref="A1:AH204"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="18"/>
@@ -1164,7 +1164,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="13" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="25" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="25" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1264,6 +1264,16 @@
       <c r="AF1" s="4" t="s">
         <v>41</v>
       </c>
+      <c r="AG1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hub_origin</t>
+        </is>
+      </c>
+      <c r="AH1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hub_brand</t>
+        </is>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -1362,6 +1372,16 @@
       <c r="AF2" s="5" t="s">
         <v>42</v>
       </c>
+      <c r="AG2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">optional</t>
+        </is>
+      </c>
+      <c r="AH2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">optional</t>
+        </is>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
@@ -1460,6 +1480,16 @@
       <c r="AF3" s="7" t="s">
         <v>75</v>
       </c>
+      <c r="AG3" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where the piece is from (dropdown). Made in Japan = the site shows 日本製 / Made in Japan for THIS piece. Branded = the site shows the brand name and no origin. Other / Unknown = the site says nothing. Blank = Unknown. Never guess.</t>
+        </is>
+      </c>
+      <c r="AH3" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brand name, e.g. Tiffany &amp; Co. Required when hub_origin is Branded; shown on the site only then. Name only — never a logo.</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
@@ -1557,6 +1587,16 @@
       </c>
       <c r="AF4" s="7" t="s">
         <v>97</v>
+      </c>
+      <c r="AG4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hub: Edit product › origin</t>
+        </is>
+      </c>
+      <c r="AH4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hub: Edit product › brand</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1631,6 +1671,16 @@
       <c r="AF5" s="9" t="s">
         <v>107</v>
       </c>
+      <c r="AG5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
+        </is>
+      </c>
+      <c r="AH5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8"/>
@@ -1703,6 +1753,16 @@
       </c>
       <c r="AF6" s="9" t="s">
         <v>112</v>
+      </c>
+      <c r="AG6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
+        </is>
+      </c>
+      <c r="AH6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11408,7 +11468,7 @@
       <c r="AF204" s="9"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Y5:Y204" type="list">
       <formula1>Lists!$A$2:$A$8</formula1>
       <formula2>0</formula2>
@@ -11429,6 +11489,10 @@
       <formula1>Lists!$E$2:$E$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="AG5:AG204" type="list">
+      <formula1>Lists!$F$2:$F$5</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11446,7 +11510,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -11468,6 +11532,11 @@
       <c r="E1" s="12" t="s">
         <v>117</v>
       </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">origin</t>
+        </is>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
@@ -11485,6 +11554,11 @@
       <c r="E2" s="13" t="s">
         <v>120</v>
       </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Made in Japan</t>
+        </is>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
@@ -11502,6 +11576,11 @@
       <c r="E3" s="13" t="s">
         <v>100</v>
       </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Branded</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
@@ -11510,6 +11589,11 @@
       <c r="B4" s="13" t="s">
         <v>124</v>
       </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
@@ -11517,6 +11601,11 @@
       </c>
       <c r="B5" s="13" t="s">
         <v>126</v>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
+        </is>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11559,7 +11648,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -11839,6 +11928,60 @@
       </c>
       <c r="E16" s="15"/>
     </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hub_origin</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">optional</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Origin</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Made in Japan / Branded / Other / Unknown. Blank = Unknown. Only Made in Japan lets the site say 日本製.</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hub_brand</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">optional</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brand</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brand name; required when hub_origin is Branded. Shown on the site only then.</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiffany &amp; Co.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/templates/cha-jewels-product-upload-template.xlsx
+++ b/public/templates/cha-jewels-product-upload-template.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="186">
   <si>
     <t xml:space="preserve">Cha Jewels product upload template</t>
   </si>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">Jewelry type (dropdown). Sets the SKU prefix and the Hub collection.</t>
   </si>
   <si>
-    <t xml:space="preserve">Metal purity for the Hub metal field (dropdown). Colour and mixed marks (WG, YG, PT900/K18) go in the description.</t>
+    <t xml:space="preserve">Metal stamp(s) exactly as stamped (dropdown, or type several separated by / e.g. PT900/K18). 750 and 18K stay as written, never K18. Colour marks (WG, YG) go in the description.</t>
   </si>
   <si>
     <t xml:space="preserve">Weight in grams (number only). Hub weight_g. Page365 weight_kg fills by formula.</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">Metal</t>
   </si>
   <si>
-    <t xml:space="preserve">K18, K14, K10, PT1000, PT950, PT900, SILVER925</t>
+    <t xml:space="preserve">One or more of K24, K18, 750, 18K, K14, K10, PT1000, PT950, PT900, PT850, PM, PM900, SILVER925 — several separated by /, order kept</t>
   </si>
   <si>
     <t xml:space="preserve">Weight (g)</t>
@@ -582,6 +582,27 @@
   </si>
   <si>
     <t xml:space="preserve">Page365 only; ignored by the Hub importer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT900/K18</t>
   </si>
 </sst>
 </file>
@@ -11474,7 +11495,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Z5:Z204" type="list">
-      <formula1>Lists!$B$2:$B$8</formula1>
+      <formula1>Lists!$B$2:$B$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="AD5:AD204" type="list">
@@ -11510,7 +11531,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -11542,8 +11563,8 @@
       <c r="A2" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>102</v>
+      <c r="B2" t="s">
+        <v>179</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>118</v>
@@ -11564,8 +11585,8 @@
       <c r="A3" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>122</v>
+      <c r="B3" t="s">
+        <v>102</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>105</v>
@@ -11586,8 +11607,8 @@
       <c r="A4" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>124</v>
+      <c r="B4" t="s">
+        <v>180</v>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
@@ -11599,8 +11620,8 @@
       <c r="A5" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>126</v>
+      <c r="B5" t="s">
+        <v>181</v>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
@@ -11612,23 +11633,53 @@
       <c r="A6" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>128</v>
+      <c r="B6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>130</v>
+      <c r="B7" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="s">
         <v>132</v>
       </c>
     </row>
@@ -11739,8 +11790,8 @@
       <c r="D5" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>102</v>
+      <c r="E5" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
